--- a/LDH_Cart.xlsx
+++ b/LDH_Cart.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AI\blood\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE69911E-8380-4F99-A8DB-46F946FF4C54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B980E5A9-F519-494A-BA48-3FC8078000E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cart细胞" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="214">
   <si>
     <t>表格 3</t>
   </si>
@@ -702,6 +702,58 @@
   </si>
   <si>
     <t>2026.05.13</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026.06.11</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>↑91.07</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>↓16.18</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>↑71.07</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>623</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>↓101</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>443</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>↑47.5</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>↑0.17</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>↑89.34</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>↑296</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>↑1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>↑265</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -1160,9 +1212,9 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>LDH!$A$4:$A$23</c:f>
+              <c:f>LDH!$A$4:$A$24</c:f>
               <c:strCache>
-                <c:ptCount val="20"/>
+                <c:ptCount val="21"/>
                 <c:pt idx="0">
                   <c:v>2026.01.19</c:v>
                 </c:pt>
@@ -1222,16 +1274,19 @@
                 </c:pt>
                 <c:pt idx="19">
                   <c:v>2026.05.13</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>2026.06.11</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>LDH!$B$4:$B$23</c:f>
+              <c:f>LDH!$B$4:$B$24</c:f>
               <c:numCache>
                 <c:formatCode>#,##0</c:formatCode>
-                <c:ptCount val="20"/>
+                <c:ptCount val="21"/>
                 <c:pt idx="0">
                   <c:v>1482</c:v>
                 </c:pt>
@@ -1291,6 +1346,9 @@
                 </c:pt>
                 <c:pt idx="19">
                   <c:v>416</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>409</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4685,16 +4743,16 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P14"/>
+  <dimension ref="A1:Q14"/>
   <sheetFormatPr defaultColWidth="16.28515625" defaultRowHeight="19.899999999999999" customHeight="1"/>
   <cols>
     <col min="1" max="10" width="16.28515625" style="1" customWidth="1"/>
-    <col min="11" max="15" width="16.28515625" style="36" customWidth="1"/>
-    <col min="16" max="17" width="16.28515625" style="1" customWidth="1"/>
-    <col min="18" max="16384" width="16.28515625" style="1"/>
+    <col min="11" max="16" width="16.28515625" style="36" customWidth="1"/>
+    <col min="17" max="18" width="16.28515625" style="1" customWidth="1"/>
+    <col min="19" max="16384" width="16.28515625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="30.95" customHeight="1">
+    <row r="1" spans="1:17" ht="30.95" customHeight="1">
       <c r="A1" s="40" t="s">
         <v>0</v>
       </c>
@@ -4713,8 +4771,9 @@
       <c r="N1" s="40"/>
       <c r="O1" s="40"/>
       <c r="P1" s="40"/>
-    </row>
-    <row r="2" spans="1:16" ht="37.15" customHeight="1">
+      <c r="Q1" s="40"/>
+    </row>
+    <row r="2" spans="1:17" ht="37.15" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -4763,8 +4822,11 @@
       <c r="P2" s="4">
         <v>45790</v>
       </c>
-    </row>
-    <row r="3" spans="1:16" ht="30" customHeight="1">
+      <c r="Q2" s="4">
+        <v>45818</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" ht="30" customHeight="1">
       <c r="A3" s="6" t="s">
         <v>8</v>
       </c>
@@ -4813,8 +4875,11 @@
       <c r="P3" s="8" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="4" spans="1:16" ht="48.75" customHeight="1">
+      <c r="Q3" s="8" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" ht="48.75" customHeight="1">
       <c r="A4" s="10" t="s">
         <v>16</v>
       </c>
@@ -4863,8 +4928,11 @@
       <c r="P4" s="12" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="5" spans="1:16" ht="48.75" customHeight="1">
+      <c r="Q4" s="12" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" ht="48.75" customHeight="1">
       <c r="A5" s="10" t="s">
         <v>20</v>
       </c>
@@ -4913,8 +4981,11 @@
       <c r="P5" s="12" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="6" spans="1:16" ht="37.5" customHeight="1">
+      <c r="Q5" s="12" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" ht="37.5" customHeight="1">
       <c r="A6" s="10" t="s">
         <v>30</v>
       </c>
@@ -4963,8 +5034,11 @@
       <c r="P6" s="12" t="s">
         <v>190</v>
       </c>
-    </row>
-    <row r="7" spans="1:16" ht="56.25" customHeight="1">
+      <c r="Q6" s="12" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" ht="56.25" customHeight="1">
       <c r="A7" s="10" t="s">
         <v>39</v>
       </c>
@@ -5013,8 +5087,11 @@
       <c r="P7" s="12" t="s">
         <v>191</v>
       </c>
-    </row>
-    <row r="8" spans="1:16" ht="51.4" customHeight="1">
+      <c r="Q7" s="12" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" ht="51.4" customHeight="1">
       <c r="A8" s="10" t="s">
         <v>48</v>
       </c>
@@ -5063,8 +5140,11 @@
       <c r="P8" s="39" t="s">
         <v>192</v>
       </c>
-    </row>
-    <row r="9" spans="1:16" ht="38.25" customHeight="1">
+      <c r="Q8" s="39" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" ht="38.25" customHeight="1">
       <c r="A9" s="10" t="s">
         <v>57</v>
       </c>
@@ -5113,8 +5193,11 @@
       <c r="P9" s="12" t="s">
         <v>193</v>
       </c>
-    </row>
-    <row r="10" spans="1:16" ht="49.5" customHeight="1">
+      <c r="Q9" s="12" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" ht="49.5" customHeight="1">
       <c r="A10" s="10" t="s">
         <v>67</v>
       </c>
@@ -5163,8 +5246,11 @@
       <c r="P10" s="12" t="s">
         <v>194</v>
       </c>
-    </row>
-    <row r="11" spans="1:16" ht="56.25" customHeight="1">
+      <c r="Q10" s="12" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" ht="56.25" customHeight="1">
       <c r="A11" s="10" t="s">
         <v>75</v>
       </c>
@@ -5213,8 +5299,11 @@
       <c r="P11" s="12" t="s">
         <v>195</v>
       </c>
-    </row>
-    <row r="12" spans="1:16" ht="58.5" customHeight="1">
+      <c r="Q11" s="12" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" ht="58.5" customHeight="1">
       <c r="A12" s="10" t="s">
         <v>84</v>
       </c>
@@ -5263,8 +5352,11 @@
       <c r="P12" s="12" t="s">
         <v>196</v>
       </c>
-    </row>
-    <row r="13" spans="1:16" ht="51.4" customHeight="1">
+      <c r="Q12" s="12" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" ht="51.4" customHeight="1">
       <c r="A13" s="10" t="s">
         <v>92</v>
       </c>
@@ -5313,8 +5405,11 @@
       <c r="P13" s="12" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="14" spans="1:16" ht="51.4" customHeight="1">
+      <c r="Q13" s="12" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" ht="51.4" customHeight="1">
       <c r="A14" s="10" t="s">
         <v>99</v>
       </c>
@@ -5363,10 +5458,13 @@
       <c r="P14" s="12" t="s">
         <v>198</v>
       </c>
+      <c r="Q14" s="12" t="s">
+        <v>213</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="A1:Q1"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.25" footer="0.25"/>
@@ -5379,7 +5477,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr defaultColWidth="27.7109375" defaultRowHeight="19.899999999999999" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="24.7109375" style="14" customWidth="1"/>
@@ -5619,7 +5717,7 @@
       <c r="D22" s="23"/>
       <c r="E22" s="23"/>
     </row>
-    <row r="23" spans="1:5" ht="19.5" customHeight="1">
+    <row r="23" spans="1:5" s="36" customFormat="1" ht="19.5" customHeight="1">
       <c r="A23" s="19" t="s">
         <v>200</v>
       </c>
@@ -5629,6 +5727,17 @@
       <c r="C23" s="23"/>
       <c r="D23" s="23"/>
       <c r="E23" s="23"/>
+    </row>
+    <row r="24" spans="1:5" ht="19.5" customHeight="1">
+      <c r="A24" s="19" t="s">
+        <v>201</v>
+      </c>
+      <c r="B24" s="22">
+        <v>409</v>
+      </c>
+      <c r="C24" s="23"/>
+      <c r="D24" s="23"/>
+      <c r="E24" s="23"/>
     </row>
   </sheetData>
   <mergeCells count="1">
